--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ23"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55545401</v>
+        <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91330</v>
+        <v>91556</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,44 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4189</v>
+        <v>4188</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Fransig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Geastrum fimbriatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>Fr.:Pers.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696313</v>
+        <v>696294</v>
       </c>
       <c r="R5" t="n">
-        <v>6643640</v>
+        <v>6643622</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1091,17 +1081,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>I barrmatta under gammal gran. Gammal barrblandskog.</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1110,34 +1105,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545401</t>
+          <t>https://artportalen.se/Sighting/137373626</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55545402</v>
+        <v>55545401</v>
       </c>
       <c r="B6" t="n">
-        <v>92869</v>
+        <v>91330</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,25 +1139,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>4189</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+          <t>Pers., nom.sanct</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1211,7 +1213,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog.</t>
+          <t>I barrmatta under gammal gran. Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,38 +1240,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545402</t>
+          <t>https://artportalen.se/Sighting/55545401</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55545404</v>
+        <v>55545402</v>
       </c>
       <c r="B7" t="n">
-        <v>93233</v>
+        <v>92869</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5964</v>
+        <v>4769</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1281,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>696297</v>
+        <v>696313</v>
       </c>
       <c r="R7" t="n">
-        <v>6643633</v>
+        <v>6643640</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1348,16 +1350,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545404</t>
+          <t>https://artportalen.se/Sighting/55545402</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132827060</v>
+        <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>93132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1365,42 +1367,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>696289</v>
+        <v>696320</v>
       </c>
       <c r="R8" t="n">
-        <v>6643730</v>
+        <v>6643729</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1424,22 +1421,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1454,70 +1451,67 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132827060</t>
+          <t>https://artportalen.se/Sighting/137373622</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132830909</v>
+        <v>55545404</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>93233</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>696293</v>
+        <v>696297</v>
       </c>
       <c r="R9" t="n">
-        <v>6643676</v>
+        <v>6643633</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1541,22 +1535,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>12:14</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,79 +1554,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830909</t>
+          <t>https://artportalen.se/Sighting/55545404</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132830902</v>
+        <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>58131</v>
+        <v>93497</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103023</v>
+        <v>5964</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Eklund, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>696274</v>
+        <v>696322</v>
       </c>
       <c r="R10" t="n">
-        <v>6643661</v>
+        <v>6643731</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1661,22 +1643,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1691,68 +1673,70 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830902</t>
+          <t>https://artportalen.se/Sighting/137373621</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55545407</v>
+        <v>132827060</v>
       </c>
       <c r="B11" t="n">
-        <v>111390</v>
+        <v>57972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219711</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>696326</v>
+        <v>696289</v>
       </c>
       <c r="R11" t="n">
-        <v>6643740</v>
+        <v>6643730</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1776,17 +1760,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,71 +1790,67 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545407</t>
+          <t>https://artportalen.se/Sighting/132827060</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132827269</v>
+        <v>132830909</v>
       </c>
       <c r="B12" t="n">
-        <v>99195</v>
+        <v>57972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>696289</v>
+        <v>696293</v>
       </c>
       <c r="R12" t="n">
-        <v>6643668</v>
+        <v>6643676</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,71 +1907,70 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132827269</t>
+          <t>https://artportalen.se/Sighting/132830909</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132827302</v>
+        <v>132830902</v>
       </c>
       <c r="B13" t="n">
-        <v>99195</v>
+        <v>58131</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ramaren, Ramaren, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>696294</v>
+        <v>696274</v>
       </c>
       <c r="R13" t="n">
-        <v>6643666</v>
+        <v>6643661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,74 +2027,68 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen, Liam Sebestyén</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132827302</t>
+          <t>https://artportalen.se/Sighting/132830902</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132830903</v>
+        <v>55545407</v>
       </c>
       <c r="B14" t="n">
-        <v>99195</v>
+        <v>111390</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>219711</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>696214</v>
+        <v>696326</v>
       </c>
       <c r="R14" t="n">
-        <v>6643713</v>
+        <v>6643740</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2134,22 +2112,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>12:37</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2164,24 +2137,24 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830903</t>
+          <t>https://artportalen.se/Sighting/55545407</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132830904</v>
+        <v>132827269</v>
       </c>
       <c r="B15" t="n">
         <v>99195</v>
@@ -2211,7 +2184,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2221,14 +2194,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>696201</v>
+        <v>696289</v>
       </c>
       <c r="R15" t="n">
-        <v>6643715</v>
+        <v>6643668</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2260,7 +2233,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2270,7 +2243,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2285,24 +2258,24 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830904</t>
+          <t>https://artportalen.se/Sighting/132827269</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132830908</v>
+        <v>132827302</v>
       </c>
       <c r="B16" t="n">
         <v>99195</v>
@@ -2332,7 +2305,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2342,14 +2315,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Ramaren, Ramaren, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>696294</v>
       </c>
       <c r="R16" t="n">
-        <v>6643676</v>
+        <v>6643666</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2381,7 +2354,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2391,7 +2364,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,68 +2379,74 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ulla Sebestyen, Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830908</t>
+          <t>https://artportalen.se/Sighting/132827302</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>55545403</v>
+        <v>132830903</v>
       </c>
       <c r="B17" t="n">
-        <v>101326</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>696313</v>
+        <v>696214</v>
       </c>
       <c r="R17" t="n">
-        <v>6643640</v>
+        <v>6643713</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2491,17 +2470,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gammal barrblandskog.</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,68 +2500,74 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545403</t>
+          <t>https://artportalen.se/Sighting/132830903</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>55545406</v>
+        <v>132830904</v>
       </c>
       <c r="B18" t="n">
-        <v>101326</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>696276</v>
+        <v>696201</v>
       </c>
       <c r="R18" t="n">
-        <v>6643760</v>
+        <v>6643715</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,12 +2591,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:36</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2621,68 +2621,74 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545406</t>
+          <t>https://artportalen.se/Sighting/132830904</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55545410</v>
+        <v>132830908</v>
       </c>
       <c r="B19" t="n">
-        <v>101326</v>
+        <v>99195</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>696326</v>
+        <v>696294</v>
       </c>
       <c r="R19" t="n">
-        <v>6643740</v>
+        <v>6643676</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2706,12 +2712,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2726,27 +2742,27 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55545410</t>
+          <t>https://artportalen.se/Sighting/132830908</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132830899</v>
+        <v>55545403</v>
       </c>
       <c r="B20" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,19 +2788,22 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>696275</v>
+        <v>696313</v>
       </c>
       <c r="R20" t="n">
-        <v>6643599</v>
+        <v>6643640</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2808,22 +2827,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:54</t>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2838,27 +2852,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830899</t>
+          <t>https://artportalen.se/Sighting/55545403</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132830900</v>
+        <v>55545406</v>
       </c>
       <c r="B21" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2884,19 +2898,22 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skarnbro, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>696261</v>
+        <v>696276</v>
       </c>
       <c r="R21" t="n">
-        <v>6643641</v>
+        <v>6643760</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2920,22 +2937,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>12:49</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2950,27 +2957,27 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830900</t>
+          <t>https://artportalen.se/Sighting/55545406</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132830905</v>
+        <v>55545410</v>
       </c>
       <c r="B22" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2996,19 +3003,22 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ramaren, Upl</t>
+          <t>Eklund, NV om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>696297</v>
+        <v>696326</v>
       </c>
       <c r="R22" t="n">
-        <v>6643754</v>
+        <v>6643740</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3032,22 +3042,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2015-10-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3062,27 +3062,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132830905</t>
+          <t>https://artportalen.se/Sighting/55545410</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55545408</v>
+        <v>132830899</v>
       </c>
       <c r="B23" t="n">
-        <v>101228</v>
+        <v>101403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3090,40 +3090,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Eklund, NV om, Upl</t>
+          <t>Skarnbro, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>696326</v>
+        <v>696275</v>
       </c>
       <c r="R23" t="n">
-        <v>6643740</v>
+        <v>6643599</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3147,12 +3144,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2015-10-07</t>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3167,18 +3174,459 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/132830899</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132830900</v>
+      </c>
+      <c r="B24" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Skarnbro, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>696261</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6643641</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830900</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132830905</v>
+      </c>
+      <c r="B25" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ramaren, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>696297</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6643754</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132830905</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>55545408</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eklund, NV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>696326</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6643740</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2015-10-07</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/55545408</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137373620</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92951</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>696313</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6643731</v>
+      </c>
+      <c r="S27" t="n">
+        <v>21</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Moa Björnberg Dillner</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137373620</t>
         </is>
       </c>
     </row>
@@ -3206,6 +3654,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ27"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,7 +1019,7 @@
         <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91556</v>
+        <v>91558</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>93132</v>
+        <v>93134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137373620</v>
       </c>
       <c r="B27" t="n">
-        <v>92951</v>
+        <v>92953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3627,6 +3627,137 @@
       <c r="AZ27" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137373620</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137387902</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92953</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>232138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gul lammticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Albatrellus citrinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Ryman</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Eklund, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>696309</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6643713</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ett stort antal fruktkroppar vid gran och hassel i örtdominerad kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Lågörtbarrskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Johan Lindell</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Johan Lindell, Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137387902</t>
         </is>
       </c>
     </row>
@@ -3658,6 +3789,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91558</v>
+        <v>91563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>93134</v>
+        <v>93140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137373620</v>
       </c>
       <c r="B27" t="n">
-        <v>92953</v>
+        <v>92958</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>137387902</v>
       </c>
       <c r="B28" t="n">
-        <v>92953</v>
+        <v>92958</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91563</v>
+        <v>91575</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>93140</v>
+        <v>93152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137373620</v>
       </c>
       <c r="B27" t="n">
-        <v>92958</v>
+        <v>92970</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>137387902</v>
       </c>
       <c r="B28" t="n">
-        <v>92958</v>
+        <v>92970</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91575</v>
+        <v>91576</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>93152</v>
+        <v>93153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137373620</v>
       </c>
       <c r="B27" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>137387902</v>
       </c>
       <c r="B28" t="n">
-        <v>92970</v>
+        <v>92971</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91576</v>
+        <v>91579</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>93153</v>
+        <v>93156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137373620</v>
       </c>
       <c r="B27" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>137387902</v>
       </c>
       <c r="B28" t="n">
-        <v>92971</v>
+        <v>92974</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 15925-2026 artfynd.xlsx
+++ b/artfynd/A 15925-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>137373626</v>
       </c>
       <c r="B5" t="n">
-        <v>91579</v>
+        <v>91583</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>137373622</v>
       </c>
       <c r="B8" t="n">
-        <v>93156</v>
+        <v>93160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>137373621</v>
       </c>
       <c r="B10" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137373620</v>
       </c>
       <c r="B27" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3635,7 +3635,7 @@
         <v>137387902</v>
       </c>
       <c r="B28" t="n">
-        <v>92974</v>
+        <v>92978</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
